--- a/artfynd/A 25729-2022 artfynd.xlsx
+++ b/artfynd/A 25729-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25729-2022 artfynd.xlsx
+++ b/artfynd/A 25729-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>73852293</v>
       </c>
       <c r="B2" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>823072.1675717889</v>
+        <v>823072</v>
       </c>
       <c r="R2" t="n">
-        <v>7285347.209936507</v>
+        <v>7285347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -800,6 +795,124 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129855259</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Maravikberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>822969</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7285373</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>två individer, varav minst en tupp.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helena Lindén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helena Lindén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25729-2022 artfynd.xlsx
+++ b/artfynd/A 25729-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73852293</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,8 +923,17 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129855259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>